--- a/files/九龙-西南九龙-维港汇 I.xlsx
+++ b/files/九龙-西南九龙-维港汇 I.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座 销控表" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3A座" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3B座" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5座" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,14 +48,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -67,7 +72,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -78,7 +83,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -89,7 +94,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -99,9 +104,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="9">
@@ -149,8 +175,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -180,7 +206,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -197,19 +223,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -227,13 +241,37 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -611,7 +649,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -24798,809 +24836,809 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 I - 1座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>68 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27&amp;28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27&amp;28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 2189呎 (4+房)
-$11,505万
+$11505万
 $52,560/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 1826呎 (4+房)
-$8,400万
+$8400万
 $46,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,992万
+$4992万
 $36,041/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,428万
+$3428万
 $36,156/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 967呎 (3房)
-$3,068万
+$3068万
 $31,727/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,888万
+$4888万
 $35,292/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,280万
+$3280万
 $34,599/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$3,050万
+$3050万
 $31,573/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,788万
+$4788万
 $34,570/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,188万
+$3188万
 $33,629/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 967呎 (3房)
-$2,980万
+$2980万
 $30,817/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,728万
+$4728万
 $34,137/呎
 (23年-09月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,150万
+$3150万
 $33,228/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 967呎 (3房)
-$2,950万
+$2950万
 $30,507/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,944万
+$4944万
 $35,700/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,147万
+$3147万
 $33,196/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,938万
+$2938万
 $30,414/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,709万
+$4709万
 $34,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,119万
+$3119万
 $32,900/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,925万
+$2925万
 $30,280/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,800万
+$4800万
 $34,660/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,214万
+$3214万
 $33,900/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,850万
+$2850万
 $29,503/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,658万
+$4658万
 $33,628/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,200万
+$3200万
 $33,755/呎
 (24年-09月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,800万
+$2800万
 $28,986/呎
 (23年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,550万
+$4550万
 $32,852/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,053万
+$3053万
 $32,200/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,770万
+$2770万
 $28,675/呎
 (23年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,538万
+$4538万
 $32,765/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,034万
+$3034万
 $32,000/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 967呎 (3房)
-$2,750万
+$2750万
 $28,438/呎
 (23年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,400万
+$4400万
 $31,769/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$3,005万
+$3005万
 $31,700/呎
 (25年-01月)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,740万
+$2740万
 $28,360/呎
 (23年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,377万
+$4377万
 $31,600/呎
 (23年-10月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,978万
+$2978万
 $31,414/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,721万
+$2721万
 $28,171/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,580万
+$4580万
 $33,069/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,956万
+$2956万
 $31,180/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,636万
+$2636万
 $27,288/呎
 (23年-07月)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,350万
+$4350万
 $31,408/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,985万
+$2985万
 $31,487/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,626万
+$2626万
 $27,184/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,320万
+$4320万
 $31,191/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,900万
+$2900万
 $30,591/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,616万
+$2616万
 $27,081/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,200万
+$4200万
 $30,325/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,929万
+$2929万
 $30,897/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,595万
+$2595万
 $26,863/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,180万
+$4180万
 $30,181/呎
 (24年-08月)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,840万
+$2840万
 $29,958/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,563万
+$2563万
 $26,532/呎
 (23年-07月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,350万
+$4350万
 $31,407/呎
 (21年-11月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,847万
+$2847万
 $30,032/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 967呎 (3房)
-$2,510万
+$2510万
 $25,957/呎
 (23年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,160万
+$4160万
 $30,036/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,847万
+$2847万
 $30,032/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,470万
+$2470万
 $25,569/呎
 (23年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,068万
+$4068万
 $29,372/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,780万
+$2780万
 $29,325/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 966呎 (3房)
-$2,458万
+$2458万
 $25,445/呎
 (23年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 1385呎 (4+房)
-$4,080万
+$4080万
 $29,458/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 948呎 (3房)
-$2,760万
+$2760万
 $29,114/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 967呎 (3房)
-$2,408万
+$2408万
 $24,902/呎
 (24年-01月)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 1320呎 (4+房)
-$4,395万
+$4395万
 $33,297/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 897呎 (3房)
-$2,900万
+$2900万
 $32,330/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 915呎 (3房)
-$2,838万
+$2838万
 $31,016/呎
 (已售)</t>
         </is>
@@ -25608,7 +25646,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -25621,895 +25659,895 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 I - 2座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>76 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>76 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1390呎 (4+房)
-$6,377万
+$6377万
 $45,874/呎
 (21年-05月)</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr"/>
-      <c r="D6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 805呎 (3房)
-$2,390万
+$2390万
 $29,689/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,515万
+$1515万
 $30,922/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,389万
+$2389万
 $30,475/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 798呎 (3房)
-$2,372万
+$2372万
 $29,724/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,467万
+$1467万
 $30,006/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,400万
+$2400万
 $30,611/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 798呎 (3房)
-$2,371万
+$2371万
 $29,716/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,516万
+$1516万
 $30,929/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,319万
+$2319万
 $29,581/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,327万
+$2327万
 $29,307/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,444万
+$1444万
 $29,533/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,362万
+$2362万
 $30,128/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,443万
+$2443万
 $30,768/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,498万
+$1498万
 $30,626/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,250万
+$2250万
 $28,693/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,299万
+$2299万
 $28,957/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,427万
+$1427万
 $29,180/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,280万
+$2280万
 $29,082/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,286万
+$2286万
 $28,785/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,418万
+$1418万
 $29,006/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,320万
+$2320万
 $29,591/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,456万
+$2456万
 $30,937/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,436万
+$1436万
 $29,306/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,253万
+$2253万
 $28,743/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,258万
+$2258万
 $28,442/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,402万
+$1402万
 $28,603/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,336万
+$2336万
 $29,790/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,343万
+$2343万
 $29,509/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,393万
+$1393万
 $28,491/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,267万
+$2267万
 $28,920/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,287万
+$2287万
 $28,802/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,393万
+$1393万
 $28,491/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,160万
+$2160万
 $27,551/呎
 (23年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,218万
+$2218万
 $27,938/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,377万
+$1377万
 $28,153/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,241万
+$2241万
 $28,578/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,205万
+$2205万
 $27,771/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,368万
+$1368万
 $27,928/呎
 (24年-02月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,227万
+$2227万
 $28,408/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,288万
+$2288万
 $28,813/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,360万
+$1360万
 $27,761/呎
 (24年-07月)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,161万
+$2161万
 $27,561/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,179万
+$2179万
 $27,440/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,444万
+$1444万
 $29,530/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,201万
+$2201万
 $28,069/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,166万
+$2166万
 $27,278/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,402万
+$1402万
 $28,675/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,096万
+$2096万
 $26,733/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,234万
+$2234万
 $28,130/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,427万
+$1427万
 $29,178/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,070万
+$2070万
 $26,403/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,222万
+$2222万
 $27,983/呎
 (21年-07月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,418万
+$1418万
 $28,944/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,192万
+$2192万
 $27,953/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,140万
+$2140万
 $26,952/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,385万
+$1385万
 $28,333/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,081万
+$2081万
 $26,546/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,140万
+$2140万
 $26,952/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,345万
+$1345万
 $27,502/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,081万
+$2081万
 $26,545/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,086万
+$2086万
 $26,272/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,361万
+$1361万
 $27,773/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,134万
+$2134万
 $27,216/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,072万
+$2072万
 $26,096/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,385万
+$1385万
 $28,262/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,121万
+$2121万
 $27,053/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,105万
+$2105万
 $26,511/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,321万
+$1321万
 $26,956/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 784呎 (3房)
-$2,020万
+$2020万
 $25,765/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="65" customHeight="1">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 794呎 (3房)
-$2,045万
+$2045万
 $25,756/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="C30" s="16" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,337万
+$1337万
 $27,335/呎
 (21年-09月)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>C | 792呎 (3房)
-$2,010万
+$2010万
 $25,379/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="65" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B31" s="16" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 750呎 (3房)
-$2,166万
+$2166万
 $28,880/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="C31" s="16" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 452呎 (2房)
-$1,390万
+$1390万
 $30,752/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D30" s="20" t="inlineStr">
         <is>
           <t>C | 749呎 (3房)
-$2,080万
+$2080万
 $27,770/呎
 (24年-01月)</t>
         </is>
@@ -26517,7 +26555,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -26530,1031 +26568,1031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 I - 3A座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3A座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 1102呎 (4+房)
-$4,130万
+$4130万
 $37,477/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 859呎 (3房)
-$3,208万
+$3208万
 $37,346/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,501万
+$2501万
 $29,958/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,482万
+$1482万
 $30,311/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,400万
+$1400万
 $28,398/呎
 (24年-11月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,466万
+$1466万
 $27,555/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,350万
+$2350万
 $28,139/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,393万
+$1393万
 $28,487/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,372万
+$1372万
 $27,839/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,437万
+$1437万
 $27,015/呎
 (24年-04月)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,326万
+$2326万
 $27,894/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,379万
+$1379万
 $28,202/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,410万
+$1410万
 $28,597/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,423万
+$1423万
 $26,748/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,414万
+$2414万
 $28,905/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,371万
+$1371万
 $28,035/呎
 (23年-07月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,410万
+$1410万
 $28,598/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,414万
+$1414万
 $26,588/呎
 (24年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,299万
+$2299万
 $27,530/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,363万
+$1363万
 $27,868/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,401万
+$1401万
 $28,427/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,467万
+$1467万
 $27,572/呎
 (21年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,385万
+$2385万
 $28,561/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,355万
+$1355万
 $27,702/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,335万
+$1335万
 $27,073/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,398万
+$1398万
 $26,272/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,427万
+$2427万
 $29,071/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,347万
+$1347万
 $27,537/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,327万
+$1327万
 $26,913/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,432万
+$1432万
 $26,919/呎
 (25年-12月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,258万
+$2258万
 $27,040/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,396万
+$1396万
 $28,555/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,319万
+$1319万
 $26,751/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,398万
+$1398万
 $26,280/呎
 (21年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,399万
+$2399万
 $28,726/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,372万
+$1372万
 $27,991/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,311万
+$1311万
 $26,593/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,356万
+$1356万
 $25,486/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,286万
+$2286万
 $27,415/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,372万
+$1372万
 $28,048/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,311万
+$1311万
 $26,593/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,381万
+$1381万
 $25,964/呎
 (21年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,315万
+$2315万
 $27,754/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,298万
+$1298万
 $26,554/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,295万
+$1295万
 $26,277/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,398万
+$1398万
 $26,284/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,260万
+$2260万
 $27,061/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,315万
+$1315万
 $26,892/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,288万
+$1288万
 $26,119/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,332万
+$1332万
 $25,035/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,287万
+$2287万
 $27,391/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,283万
+$1283万
 $26,186/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,368万
+$1368万
 $27,748/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,382万
+$1382万
 $25,973/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,178万
+$2178万
 $26,087/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,275万
+$1275万
 $26,083/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,304万
+$1304万
 $26,455/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,406万
+$1406万
 $26,436/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,260万
+$2260万
 $27,066/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,292万
+$1292万
 $26,359/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,296万
+$1296万
 $26,297/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,308万
+$1308万
 $24,588/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,206万
+$2206万
 $26,421/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,284万
+$1284万
 $26,203/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,257万
+$1257万
 $25,503/呎
 (26年-05月)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,333万
+$1333万
 $25,053/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,233万
+$2233万
 $26,776/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,284万
+$1284万
 $26,207/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,305万
+$1305万
 $26,461/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,349万
+$1349万
 $25,358/呎
 (21年-03月)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,193万
+$2193万
 $26,295/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,308万
+$1308万
 $26,686/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,305万
+$1305万
 $26,461/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,292万
+$1292万
 $24,295/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,259万
+$2259万
 $27,091/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,238万
+$1238万
 $25,264/呎
 (26年-04月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,289万
+$1289万
 $26,144/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,277万
+$1277万
 $24,008/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,105万
+$2105万
 $25,206/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,230万
+$1230万
 $25,163/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,281万
+$1281万
 $25,990/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,325万
+$1325万
 $24,909/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 834呎 (3房)
-$2,184万
+$2184万
 $26,182/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 489呎 (2房)
-$1,277万
+$1277万
 $26,109/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,220万
+$1220万
 $24,753/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,317万
+$1317万
 $24,760/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 835呎 (3房)
-$2,080万
+$2080万
 $24,905/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 490呎 (2房)
-$1,231万
+$1231万
 $25,125/呎
 (24年-03月)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 493呎 (2房)
-$1,213万
+$1213万
 $24,605/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 532呎 (2房)
-$1,309万
+$1309万
 $24,612/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 789呎 (3房)
-$2,258万
+$2258万
 $28,623/呎
 (21年-07月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 452呎 (2房)
-$1,274万
+$1274万
 $28,189/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 455呎 (2房)
-$1,310万
+$1310万
 $28,802/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 494呎 (2房)
-$1,457万
+$1457万
 $29,496/呎
 (23年-12月)</t>
         </is>
@@ -27562,7 +27600,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -27575,153 +27613,153 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 I - 3B座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3B座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>192 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>184 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H4" s="19" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I4" s="19" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,580万
+$1580万
 $26,466/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $800万
@@ -27729,7 +27767,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $818万
@@ -27737,15 +27775,15 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,200万
+$1200万
 $26,786/呎
 (25年-04月)</t>
         </is>
       </c>
-      <c r="F6" s="16" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $798万
@@ -27753,7 +27791,7 @@
 (25年-10月)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $827万
@@ -27761,7 +27799,7 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $829万
@@ -27769,7 +27807,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="I6" s="18" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $918万
@@ -27778,21 +27816,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,513万
+$1513万
 $25,341/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $928万
@@ -27800,7 +27838,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $874万
@@ -27808,15 +27846,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,068万
+$1068万
 $23,839/呎
 (25年-05月)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $874万
@@ -27824,7 +27862,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $871万
@@ -27832,7 +27870,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H6" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $822万
@@ -27840,7 +27878,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $752万
@@ -27849,21 +27887,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,604万
+$1604万
 $26,864/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $850万
@@ -27871,7 +27909,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $873万
@@ -27879,15 +27917,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,075万
+$1075万
 $24,000/呎
 (25年-04月)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $821万
@@ -27895,7 +27933,7 @@
 (21年-03月)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $854万
@@ -27903,7 +27941,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H7" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $841万
@@ -27911,7 +27949,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I8" s="18" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $891万
@@ -27920,21 +27958,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,469万
+$1469万
 $24,600/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $901万
@@ -27942,7 +27980,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $885万
@@ -27950,15 +27988,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,069万
+$1069万
 $23,862/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $849万
@@ -27966,7 +28004,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $846万
@@ -27974,7 +28012,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H8" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $833万
@@ -27982,7 +28020,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I9" s="18" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $882万
@@ -27991,21 +28029,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,478万
+$1478万
 $24,758/呎
 (24年-06月)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $869万
@@ -28013,7 +28051,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $880万
@@ -28021,15 +28059,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,162万
+$1162万
 $25,936/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $808万
@@ -28037,7 +28075,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $841万
@@ -28045,7 +28083,7 @@
 (26年-06月)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $828万
@@ -28053,7 +28091,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I10" s="18" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $877万
@@ -28062,21 +28100,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,469万
+$1469万
 $24,611/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $832万
@@ -28084,7 +28122,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $875万
@@ -28092,15 +28130,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,048万
+$1048万
 $23,393/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $839万
@@ -28108,7 +28146,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $836万
@@ -28116,7 +28154,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H10" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $823万
@@ -28124,7 +28162,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I11" s="18" t="inlineStr">
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $872万
@@ -28133,21 +28171,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,461万
+$1461万
 $24,464/呎
 (24年-05月)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $848万
@@ -28155,7 +28193,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $833万
@@ -28163,15 +28201,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,141万
+$1141万
 $25,475/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $834万
@@ -28179,7 +28217,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $831万
@@ -28187,7 +28225,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H11" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $818万
@@ -28195,7 +28233,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $668万
@@ -28204,21 +28242,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,270万
+$1270万
 $21,273/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $880万
@@ -28226,7 +28264,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $865万
@@ -28234,15 +28272,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,057万
+$1057万
 $23,589/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $794万
@@ -28250,7 +28288,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $826万
@@ -28258,7 +28296,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H12" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $779万
@@ -28266,7 +28304,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I13" s="18" t="inlineStr">
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $862万
@@ -28275,21 +28313,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,260万
+$1260万
 $21,106/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $817万
@@ -28297,7 +28335,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $819万
@@ -28305,15 +28343,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,163万
+$1163万
 $25,950/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $824万
@@ -28321,7 +28359,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $812万
@@ -28329,7 +28367,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $809万
@@ -28337,7 +28375,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $660万
@@ -28346,21 +28384,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,435万
+$1435万
 $24,029/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $869万
@@ -28368,7 +28406,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $814万
@@ -28376,15 +28414,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,055万
+$1055万
 $23,549/呎
 (24年-12月)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $819万
@@ -28392,7 +28430,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $778万
@@ -28400,7 +28438,7 @@
 (25年-08月)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H14" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $804万
@@ -28408,7 +28446,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $656万
@@ -28417,21 +28455,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,479万
+$1479万
 $24,770/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $833万
@@ -28439,7 +28477,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $814万
@@ -28447,15 +28485,15 @@
 (21年-03月)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,040万
+$1040万
 $23,214/呎
 (25年-03月)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $784万
@@ -28463,7 +28501,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $812万
@@ -28471,7 +28509,7 @@
 (21年-03月)</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H15" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $804万
@@ -28479,7 +28517,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I16" s="18" t="inlineStr">
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $852万
@@ -28488,21 +28526,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,461万
+$1461万
 $24,477/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $859万
@@ -28510,7 +28548,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $805万
@@ -28518,15 +28556,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,108万
+$1108万
 $24,725/呎
 (21年-12月)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $809万
@@ -28534,7 +28572,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $802万
@@ -28542,7 +28580,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="H16" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $794万
@@ -28550,7 +28588,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $711万
@@ -28559,21 +28597,21 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,248万
+$1248万
 $20,905/呎
 (25年-02月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $854万
@@ -28581,7 +28619,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $835万
@@ -28589,15 +28627,15 @@
 (25年-11月)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,101万
+$1101万
 $24,578/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $804万
@@ -28605,7 +28643,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $797万
@@ -28613,7 +28651,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="H17" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $756万
@@ -28621,7 +28659,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $698万
@@ -28630,21 +28668,21 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,444万
+$1444万
 $24,187/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $849万
@@ -28652,7 +28690,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $830万
@@ -28660,15 +28698,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,095万
+$1095万
 $24,432/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $799万
@@ -28676,7 +28714,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $767万
@@ -28684,7 +28722,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="H18" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $752万
@@ -28692,7 +28730,7 @@
 (26年-04月)</t>
         </is>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $694万
@@ -28701,21 +28739,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,375万
+$1375万
 $23,034/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $844万
@@ -28723,7 +28761,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $825万
@@ -28731,15 +28769,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,088万
+$1088万
 $24,287/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $795万
@@ -28747,7 +28785,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $788万
@@ -28755,7 +28793,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="H19" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $780万
@@ -28763,7 +28801,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $661万
@@ -28772,21 +28810,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,367万
+$1367万
 $22,896/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $849万
@@ -28794,7 +28832,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $820万
@@ -28802,15 +28840,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,082万
+$1082万
 $24,143/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $790万
@@ -28818,7 +28856,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $750万
@@ -28826,7 +28864,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H20" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $743万
@@ -28834,7 +28872,7 @@
 (21年-03月)</t>
         </is>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $686万
@@ -28843,21 +28881,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,384万
+$1384万
 $23,187/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $834万
@@ -28865,7 +28903,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $781万
@@ -28873,15 +28911,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,075万
+$1075万
 $23,998/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $785万
@@ -28889,7 +28927,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $779万
@@ -28897,7 +28935,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $771万
@@ -28905,7 +28943,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I22" s="16" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $682万
@@ -28914,21 +28952,21 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,410万
+$1410万
 $23,615/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $794万
@@ -28936,7 +28974,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $810万
@@ -28944,15 +28982,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,075万
+$1075万
 $23,998/呎
 (26年-01月)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $781万
@@ -28960,7 +28998,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $774万
@@ -28968,7 +29006,7 @@
 (26年-05月)</t>
         </is>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $766万
@@ -28976,7 +29014,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $686万
@@ -28985,21 +29023,21 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,351万
+$1351万
 $22,625/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $829万
@@ -29007,7 +29045,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $810万
@@ -29015,15 +29053,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,075万
+$1075万
 $23,998/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $781万
@@ -29031,7 +29069,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $774万
@@ -29039,7 +29077,7 @@
 (25年-12月)</t>
         </is>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $766万
@@ -29047,7 +29085,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I24" s="16" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $678万
@@ -29056,21 +29094,21 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,393万
+$1393万
 $23,334/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $794万
@@ -29078,7 +29116,7 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $801万
@@ -29086,15 +29124,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,128万
+$1128万
 $25,170/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $771万
@@ -29102,7 +29140,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $765万
@@ -29110,7 +29148,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>G | 319呎 (1房)
 $739万
@@ -29118,7 +29156,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $678万
@@ -29127,21 +29165,21 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,327万
+$1327万
 $22,223/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $814万
@@ -29149,7 +29187,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $797万
@@ -29157,15 +29195,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,076万
+$1076万
 $24,009/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F26" s="16" t="inlineStr">
+      <c r="F25" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $768万
@@ -29173,7 +29211,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G26" s="16" t="inlineStr">
+      <c r="G25" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $728万
@@ -29181,7 +29219,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $721万
@@ -29189,7 +29227,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I26" s="16" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $667万
@@ -29198,21 +29236,21 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,319万
+$1319万
 $22,090/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $775万
@@ -29220,7 +29258,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $787万
@@ -29228,15 +29266,15 @@
 (26年-01月)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,088万
+$1088万
 $24,296/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F27" s="16" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>E | 320呎 (1房)
 $766万
@@ -29244,7 +29282,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G26" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $724万
@@ -29252,7 +29290,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $748万
@@ -29260,7 +29298,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>H | 278呎 (开放式)
 $645万
@@ -29269,21 +29307,21 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 597呎 (2房)
-$1,337万
+$1337万
 $22,401/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 308呎 (1房)
 $804万
@@ -29291,7 +29329,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 320呎 (1房)
 $793万
@@ -29299,15 +29337,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 448呎 (2房)
-$1,069万
+$1069万
 $23,866/呎
 (已售)</t>
         </is>
       </c>
-      <c r="F28" s="16" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>E | 319呎 (1房)
 $764万
@@ -29315,7 +29353,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G28" s="16" t="inlineStr">
+      <c r="G27" s="20" t="inlineStr">
         <is>
           <t>F | 320呎 (1房)
 $751万
@@ -29323,7 +29361,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>G | 320呎 (1房)
 $744万
@@ -29331,7 +29369,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I28" s="16" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>H | 277呎 (开放式)
 $643万
@@ -29340,21 +29378,21 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 560呎 (2房)
-$1,537万
+$1537万
 $27,451/呎
 (24年-04月)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 $913万
@@ -29362,7 +29400,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 298呎 (1房)
 $898万
@@ -29370,15 +29408,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 411呎 (2房)
-$1,168万
+$1168万
 $28,418/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="F29" s="16" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 298呎 (1房)
 $787万
@@ -29386,7 +29424,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 298呎 (1房)
 $772万
@@ -29394,7 +29432,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 298呎 (1房)
 $731万
@@ -29402,7 +29440,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="I29" s="18" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 256呎 (开放式)
 招标单位
@@ -29413,7 +29451,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -29426,1031 +29464,1031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>维港滙 I - 5座 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>5座 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>94 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 936呎 (3房)
-$3,300万
+$3300万
 $35,256/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 958呎 (3房)
-$3,168万
+$3168万
 $33,069/呎
 (24年-01月)</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,470万
+$1470万
 $28,157/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,306万
+$1306万
 $29,147/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,291万
+$1291万
 $28,826/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,416万
+$1416万
 $26,418/呎
 (24年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,441万
+$1441万
 $27,605/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,311万
+$1311万
 $29,259/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,243万
+$1243万
 $27,754/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,419万
+$1419万
 $26,474/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,427万
+$1427万
 $27,332/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,214万
+$1214万
 $27,105/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,254万
+$1254万
 $27,982/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,405万
+$1405万
 $26,212/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,401万
+$1401万
 $26,846/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,290万
+$1290万
 $28,797/呎
 (25年-06月)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,194万
+$1194万
 $26,648/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,397万
+$1397万
 $26,057/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,393万
+$1393万
 $26,688/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,200万
+$1200万
 $26,784/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,202万
+$1202万
 $26,820/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,448万
+$1448万
 $27,019/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,479万
+$1479万
 $28,328/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,193万
+$1193万
 $26,623/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,194万
+$1194万
 $26,659/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,380万
+$1380万
 $25,745/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,377万
+$1377万
 $26,370/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,186万
+$1186万
 $26,464/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,173万
+$1173万
 $26,175/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,372万
+$1372万
 $25,592/呎
 (25年-08月)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,368万
+$1368万
 $26,213/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,173万
+$1173万
 $26,177/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,195万
+$1195万
 $26,668/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,422万
+$1422万
 $26,539/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,436万
+$1436万
 $27,508/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,246万
+$1246万
 $27,808/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,209万
+$1209万
 $26,996/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,355万
+$1355万
 $25,288/呎
 (21年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,376万
+$1376万
 $26,368/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,166万
+$1166万
 $26,020/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,159万
+$1159万
 $25,864/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,355万
+$1355万
 $25,288/呎
 (21年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,386万
+$1386万
 $26,542/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,208万
+$1208万
 $26,970/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,159万
+$1159万
 $25,875/呎
 (25年-12月)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,339万
+$1339万
 $24,988/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,352万
+$1352万
 $25,910/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,195万
+$1195万
 $26,677/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,138万
+$1138万
 $25,404/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,331万
+$1331万
 $24,838/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,369万
+$1369万
 $26,226/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,138万
+$1138万
 $25,407/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,131万
+$1131万
 $25,252/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,413万
+$1413万
 $26,368/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,304万
+$1304万
 $24,978/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,160万
+$1160万
 $25,887/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,174万
+$1174万
 $26,202/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,340万
+$1340万
 $24,998/呎
 (21年-09月)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,320万
+$1320万
 $25,293/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,125万
+$1125万
 $25,104/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,167万
+$1167万
 $26,043/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,364万
+$1364万
 $25,452/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,345万
+$1345万
 $25,760/呎
 (25年-11月)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,124万
+$1124万
 $25,079/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,111万
+$1111万
 $24,804/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,324万
+$1324万
 $24,702/呎
 (25年-10月)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,369万
+$1369万
 $26,224/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,160万
+$1160万
 $25,890/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,153万
+$1153万
 $25,732/呎
 (25年-08月)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,292万
+$1292万
 $24,108/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,312万
+$1312万
 $25,138/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,188万
+$1188万
 $26,511/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,125万
+$1125万
 $25,116/呎
 (21年-03月)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,316万
+$1316万
 $24,554/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,313万
+$1313万
 $25,151/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,098万
+$1098万
 $24,511/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,139万
+$1139万
 $25,430/呎
 (26年-02月)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,277万
+$1277万
 $23,822/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,274万
+$1274万
 $24,399/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C26" s="16" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,119万
+$1119万
 $24,973/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,085万
+$1085万
 $24,216/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E26" s="16" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,355万
+$1355万
 $25,287/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,266万
+$1266万
 $24,253/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,133万
+$1133万
 $25,279/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D27" s="16" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,119万
+$1119万
 $24,976/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E27" s="16" t="inlineStr">
+      <c r="E26" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,262万
+$1262万
 $23,538/呎
 (已售)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 522呎 (2房)
-$1,313万
+$1313万
 $25,149/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C28" s="16" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 448呎 (2房)
-$1,126万
+$1126万
 $25,130/呎
 (已售)</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>C | 448呎 (2房)
-$1,099万
+$1099万
 $24,527/呎
 (已售)</t>
         </is>
       </c>
-      <c r="E28" s="16" t="inlineStr">
+      <c r="E27" s="20" t="inlineStr">
         <is>
           <t>D | 536呎 (2房)
-$1,285万
+$1285万
 $23,975/呎
 (21年-11月)</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 484呎 (2房)
-$1,439万
+$1439万
 $29,731/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C29" s="16" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 410呎 (2房)
-$1,120万
+$1120万
 $27,317/呎
 (23年-11月)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 410呎 (2房)
-$1,100万
+$1100万
 $26,829/呎
 (23年-08月)</t>
         </is>
       </c>
-      <c r="E29" s="16" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 498呎 (2房)
-$1,383万
+$1383万
 $27,767/呎
 (已售)</t>
         </is>
@@ -30458,7 +30496,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
